--- a/documents/2026-09-Evergreen.xlsx
+++ b/documents/2026-09-Evergreen.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xPrecisco\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30ADABDB-0A01-4A5A-A297-59D0AC200DD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7E9BE5-245E-4FEE-892F-010BC3E2363F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Freight" sheetId="1" r:id="rId1"/>
+    <sheet name="Surcharge" sheetId="2" r:id="rId2"/>
+    <sheet name="GRR Intra Asia" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Freight!$A$1:$E$110</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
   <extLst>

--- a/documents/2026-09-Evergreen.xlsx
+++ b/documents/2026-09-Evergreen.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xPrecisco\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7E9BE5-245E-4FEE-892F-010BC3E2363F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52004991-6A58-4471-AAE3-048188C50A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Freight" sheetId="1" r:id="rId1"/>
-    <sheet name="Surcharge" sheetId="2" r:id="rId2"/>
-    <sheet name="GRR Intra Asia" sheetId="3" r:id="rId3"/>
+    <sheet name="Shipping Rates" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Freight!$A$1:$E$110</definedName>
-  </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -30,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="183">
   <si>
     <t>Place of Delivery</t>
   </si>
@@ -44,18 +41,30 @@
     <t>OCEAN FREIGHT 40ft HQ (USD)</t>
   </si>
   <si>
-    <t>Remarks / Surcharges</t>
+    <t>Remarks / Inclusions</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
   <si>
     <t>NANSHA 南沙 -NSD service only</t>
   </si>
   <si>
+    <t>B/L &amp; B/L Surrender Fee, Seal</t>
+  </si>
+  <si>
+    <t>Asia</t>
+  </si>
+  <si>
     <t>QINGDAO, SHANDONG</t>
   </si>
   <si>
     <t>NINGBO, ZHEJIANG</t>
   </si>
   <si>
+    <t>SHANGHAI 上海</t>
+  </si>
+  <si>
     <t>SHE KOU (SHENZHEN)</t>
   </si>
   <si>
@@ -176,15 +185,24 @@
     <t>LAT KRABANG</t>
   </si>
   <si>
+    <t>B/L &amp; B/L Surrender Fee, Seal, Inland</t>
+  </si>
+  <si>
     <t>SONGKHLA</t>
   </si>
   <si>
-    <t>BANGKOK | PAT</t>
+    <t>NIL</t>
+  </si>
+  <si>
+    <t>BANGKOK | PAT 300 450 450</t>
   </si>
   <si>
     <t>HO CHI MINH (CAT LAI) (include CIC/D)</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t>HAIPHONG (include CIC/D)</t>
   </si>
   <si>
@@ -239,6 +257,12 @@
     <t>NHAVA SHEVA (INNXV)</t>
   </si>
   <si>
+    <t>B/L &amp; B/L Surrender Fee, Seal, DIH if is INLAND</t>
+  </si>
+  <si>
+    <t>India Sub-Con</t>
+  </si>
+  <si>
     <t>BENGALURU / BANGALORE (INICB)</t>
   </si>
   <si>
@@ -281,6 +305,9 @@
     <t>MULUND (INCMN)</t>
   </si>
   <si>
+    <t>NO SVC</t>
+  </si>
+  <si>
     <t>NEW DELHI - TUGHLAKABAD (INNDI)</t>
   </si>
   <si>
@@ -308,6 +335,12 @@
     <t>JEBEL ALI (AEJBA)</t>
   </si>
   <si>
+    <t>Suspension</t>
+  </si>
+  <si>
+    <t>Middle East</t>
+  </si>
+  <si>
     <t>ABU DHABI (AEABU)</t>
   </si>
   <si>
@@ -350,6 +383,9 @@
     <t>AQABA (JOAQB)</t>
   </si>
   <si>
+    <t>Red Sea</t>
+  </si>
+  <si>
     <t>SOKHNA (EGSOK)</t>
   </si>
   <si>
@@ -362,45 +398,27 @@
     <t>DURBAN (ZADRB)</t>
   </si>
   <si>
+    <t>Rates subject to THC/L, ISOCC, Seal, BL and AFR manifest filing</t>
+  </si>
+  <si>
+    <t>Africa</t>
+  </si>
+  <si>
     <t>CAPE TOWN (ZACAP)</t>
   </si>
   <si>
     <t>Johannesburg</t>
   </si>
   <si>
+    <t>Rates subject to THC/L, ISOCC, Seal, BL and AFR manifest filing, DIH at POD</t>
+  </si>
+  <si>
     <t>DAR ES SALAAM (TZDFQ)</t>
   </si>
   <si>
     <t>MOMBASA (KEMWA)</t>
   </si>
   <si>
-    <t>NIL</t>
-  </si>
-  <si>
-    <t>NO SVC</t>
-  </si>
-  <si>
-    <t>Suspension</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>B/L &amp; B/L Surrender Fee, Seal</t>
-  </si>
-  <si>
-    <t>B/L &amp; B/L Surrender Fee, Seal, Inland</t>
-  </si>
-  <si>
-    <t>B/L &amp; B/L Surrender Fee, Seal, DIH if is INLAND</t>
-  </si>
-  <si>
-    <t>Rates subject to THC/L, ISOCC, Seal, BL and AFR manifest filing</t>
-  </si>
-  <si>
-    <t>Rates subject to THC/L, ISOCC, Seal, BL and AFR manifest filing, DIH at POD</t>
-  </si>
-  <si>
     <t>TO: WHOM IT MAY CONCERN</t>
   </si>
   <si>
@@ -492,9 +510,6 @@
   </si>
   <si>
     <t>Evergreen Marine Asia Pte Ltd</t>
-  </si>
-  <si>
-    <t>Business Department</t>
   </si>
   <si>
     <t>Date : 16 Mar 2026</t>
@@ -578,10 +593,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -684,7 +696,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -716,27 +728,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -768,24 +762,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -962,16 +938,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="25" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="68" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
+    <col min="2" max="3" width="27" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="78" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -987,10 +964,13 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>150</v>
@@ -1002,12 +982,15 @@
         <v>250</v>
       </c>
       <c r="E2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>100</v>
@@ -1019,12 +1002,15 @@
         <v>180</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -1036,12 +1022,15 @@
         <v>150</v>
       </c>
       <c r="E4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>100</v>
@@ -1053,148 +1042,175 @@
         <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6">
+        <v>100</v>
+      </c>
+      <c r="C6">
+        <v>150</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
         <v>250</v>
       </c>
-      <c r="C6">
+      <c r="C7">
         <v>400</v>
       </c>
-      <c r="D6">
+      <c r="D7">
         <v>400</v>
       </c>
-      <c r="E6" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
         <v>120</v>
       </c>
-      <c r="C7">
+      <c r="C8">
         <v>180</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>180</v>
       </c>
-      <c r="E7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
         <v>100</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>160</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>160</v>
       </c>
-      <c r="E8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9">
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10">
         <v>200</v>
       </c>
-      <c r="C9">
+      <c r="C10">
         <v>260</v>
       </c>
-      <c r="D9">
+      <c r="D10">
         <v>260</v>
       </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10">
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11">
         <v>50</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>80</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>80</v>
       </c>
-      <c r="E10" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11">
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12">
         <v>900</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>1100</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>1100</v>
       </c>
-      <c r="E11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
         <v>300</v>
       </c>
-      <c r="C12">
+      <c r="C13">
         <v>300</v>
       </c>
-      <c r="D12">
+      <c r="D13">
         <v>300</v>
       </c>
-      <c r="E12" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>350</v>
-      </c>
-      <c r="C13">
-        <v>450</v>
-      </c>
-      <c r="D13">
-        <v>450</v>
-      </c>
       <c r="E13" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <v>350</v>
@@ -1206,46 +1222,55 @@
         <v>450</v>
       </c>
       <c r="E14" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15">
+        <v>350</v>
+      </c>
+      <c r="C15">
+        <v>450</v>
+      </c>
+      <c r="D15">
+        <v>450</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16">
         <v>300</v>
       </c>
-      <c r="C15">
+      <c r="C16">
         <v>400</v>
       </c>
-      <c r="D15">
+      <c r="D16">
         <v>400</v>
       </c>
-      <c r="E15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16">
-        <v>200</v>
-      </c>
-      <c r="C16">
-        <v>250</v>
-      </c>
-      <c r="D16">
-        <v>250</v>
-      </c>
       <c r="E16" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B17">
         <v>200</v>
@@ -1257,97 +1282,115 @@
         <v>250</v>
       </c>
       <c r="E17" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B18">
+        <v>200</v>
+      </c>
+      <c r="C18">
+        <v>250</v>
+      </c>
+      <c r="D18">
+        <v>250</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
         <v>800</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>1200</v>
       </c>
-      <c r="D18">
+      <c r="D19">
         <v>1200</v>
       </c>
-      <c r="E18" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19">
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20">
         <v>200</v>
       </c>
-      <c r="C19">
+      <c r="C20">
         <v>250</v>
       </c>
-      <c r="D19">
+      <c r="D20">
         <v>250</v>
       </c>
-      <c r="E19" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20">
-        <v>300</v>
-      </c>
-      <c r="C20">
-        <v>400</v>
-      </c>
-      <c r="D20">
-        <v>400</v>
-      </c>
       <c r="E20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>300</v>
       </c>
       <c r="C21">
+        <v>400</v>
+      </c>
+      <c r="D21">
+        <v>400</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
         <v>300</v>
       </c>
-      <c r="D21">
+      <c r="C22">
         <v>300</v>
       </c>
-      <c r="E21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22">
-        <v>1100</v>
-      </c>
-      <c r="C22">
-        <v>2000</v>
-      </c>
       <c r="D22">
-        <v>2000</v>
+        <v>300</v>
       </c>
       <c r="E22" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B23">
         <v>1100</v>
@@ -1359,46 +1402,55 @@
         <v>2000</v>
       </c>
       <c r="E23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24">
+        <v>1100</v>
+      </c>
+      <c r="C24">
+        <v>2000</v>
+      </c>
+      <c r="D24">
+        <v>2000</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25">
         <v>80</v>
       </c>
-      <c r="C24">
+      <c r="C25">
         <v>160</v>
       </c>
-      <c r="D24">
+      <c r="D25">
         <v>160</v>
       </c>
-      <c r="E24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25">
-        <v>120</v>
-      </c>
-      <c r="C25">
-        <v>240</v>
-      </c>
-      <c r="D25">
-        <v>240</v>
-      </c>
       <c r="E25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B26">
         <v>120</v>
@@ -1410,100 +1462,118 @@
         <v>240</v>
       </c>
       <c r="E26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B27">
+        <v>120</v>
+      </c>
+      <c r="C27">
+        <v>240</v>
+      </c>
+      <c r="D27">
+        <v>240</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28">
         <v>310</v>
       </c>
-      <c r="C27">
+      <c r="C28">
         <v>500</v>
       </c>
-      <c r="D27">
+      <c r="D28">
         <v>500</v>
       </c>
-      <c r="E27" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28">
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29">
         <v>410</v>
       </c>
-      <c r="C28">
+      <c r="C29">
         <v>600</v>
       </c>
-      <c r="D28">
+      <c r="D29">
         <v>600</v>
       </c>
-      <c r="E28" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29">
+      <c r="E29" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30">
         <v>260</v>
       </c>
-      <c r="C29">
+      <c r="C30">
         <v>400</v>
       </c>
-      <c r="D29">
+      <c r="D30">
         <v>400</v>
       </c>
-      <c r="E29" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30">
+      <c r="E30" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31">
         <v>150</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>300</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>300</v>
       </c>
-      <c r="E30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31">
+      <c r="E31" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32">
         <v>450</v>
-      </c>
-      <c r="C31">
-        <v>500</v>
-      </c>
-      <c r="D31">
-        <v>500</v>
-      </c>
-      <c r="E31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32">
-        <v>350</v>
       </c>
       <c r="C32">
         <v>500</v>
@@ -1512,80 +1582,95 @@
         <v>500</v>
       </c>
       <c r="E32" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B33">
+        <v>350</v>
+      </c>
+      <c r="C33">
+        <v>500</v>
+      </c>
+      <c r="D33">
+        <v>500</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34">
         <v>650</v>
       </c>
-      <c r="C33">
+      <c r="C34">
         <v>1250</v>
       </c>
-      <c r="D33">
+      <c r="D34">
         <v>1250</v>
       </c>
-      <c r="E33" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34">
+      <c r="E34" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35">
         <v>440</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <v>880</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <v>880</v>
       </c>
-      <c r="E34" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35">
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36">
         <v>540</v>
       </c>
-      <c r="C35">
+      <c r="C36">
         <v>1080</v>
       </c>
-      <c r="D35">
+      <c r="D36">
         <v>1080</v>
       </c>
-      <c r="E35" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36">
-        <v>640</v>
-      </c>
-      <c r="C36">
-        <v>1280</v>
-      </c>
-      <c r="D36">
-        <v>1280</v>
-      </c>
       <c r="E36" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B37">
         <v>640</v>
@@ -1597,179 +1682,215 @@
         <v>1280</v>
       </c>
       <c r="E37" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B38">
-        <v>540</v>
+        <v>640</v>
       </c>
       <c r="C38">
-        <v>1080</v>
+        <v>1280</v>
       </c>
       <c r="D38">
-        <v>1080</v>
+        <v>1280</v>
       </c>
       <c r="E38" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B39">
         <v>540</v>
       </c>
       <c r="C39">
+        <v>1080</v>
+      </c>
+      <c r="D39">
+        <v>1080</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40">
+        <v>540</v>
+      </c>
+      <c r="C40">
         <v>980</v>
       </c>
-      <c r="D39">
+      <c r="D40">
         <v>980</v>
       </c>
-      <c r="E39" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40">
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>47</v>
+      </c>
+      <c r="B41">
         <v>790</v>
       </c>
-      <c r="C40">
+      <c r="C41">
         <v>1480</v>
       </c>
-      <c r="D40">
+      <c r="D41">
         <v>1480</v>
       </c>
-      <c r="E40" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>44</v>
-      </c>
-      <c r="B41">
+      <c r="E41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42">
         <v>540</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>980</v>
       </c>
-      <c r="D41">
+      <c r="D42">
         <v>980</v>
       </c>
-      <c r="E41" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42">
+      <c r="E42" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>49</v>
+      </c>
+      <c r="B43">
         <v>180</v>
       </c>
-      <c r="C42">
+      <c r="C43">
         <v>220</v>
       </c>
-      <c r="D42">
+      <c r="D43">
         <v>220</v>
       </c>
-      <c r="E42" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43">
+      <c r="E43" t="s">
+        <v>7</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44">
         <v>30</v>
       </c>
-      <c r="C43">
+      <c r="C44">
         <v>70</v>
       </c>
-      <c r="D43">
+      <c r="D44">
         <v>70</v>
       </c>
-      <c r="E43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>47</v>
-      </c>
-      <c r="B44">
+      <c r="E44" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>51</v>
+      </c>
+      <c r="B45">
         <v>250</v>
       </c>
-      <c r="C44">
+      <c r="C45">
         <v>400</v>
       </c>
-      <c r="D44">
+      <c r="D45">
         <v>400</v>
       </c>
-      <c r="E44" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" t="s">
-        <v>114</v>
-      </c>
-      <c r="C45" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" t="s">
-        <v>114</v>
-      </c>
       <c r="E45" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46">
-        <v>300</v>
-      </c>
-      <c r="C46">
-        <v>450</v>
-      </c>
-      <c r="D46">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+      <c r="C46" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" t="s">
+        <v>55</v>
+      </c>
+      <c r="F46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B47">
         <v>120</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="D47">
         <v>200</v>
       </c>
       <c r="E47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B48">
         <v>120</v>
@@ -1781,12 +1902,15 @@
         <v>200</v>
       </c>
       <c r="E48" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="B49">
         <v>300</v>
@@ -1798,12 +1922,15 @@
         <v>600</v>
       </c>
       <c r="E49" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="B50">
         <v>400</v>
@@ -1815,12 +1942,15 @@
         <v>700</v>
       </c>
       <c r="E50" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B51">
         <v>250</v>
@@ -1832,12 +1962,15 @@
         <v>500</v>
       </c>
       <c r="E51" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B52">
         <v>300</v>
@@ -1849,12 +1982,15 @@
         <v>600</v>
       </c>
       <c r="E52" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B53">
         <v>350</v>
@@ -1866,12 +2002,15 @@
         <v>600</v>
       </c>
       <c r="E53" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B54">
         <v>200</v>
@@ -1883,12 +2022,15 @@
         <v>300</v>
       </c>
       <c r="E54" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B55">
         <v>140</v>
@@ -1900,12 +2042,15 @@
         <v>240</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B56">
         <v>180</v>
@@ -1917,12 +2062,15 @@
         <v>200</v>
       </c>
       <c r="E56" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B57">
         <v>200</v>
@@ -1934,12 +2082,15 @@
         <v>360</v>
       </c>
       <c r="E57" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B58">
         <v>360</v>
@@ -1951,12 +2102,15 @@
         <v>500</v>
       </c>
       <c r="E58" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B59">
         <v>400</v>
@@ -1968,12 +2122,15 @@
         <v>600</v>
       </c>
       <c r="E59" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B60">
         <v>400</v>
@@ -1985,12 +2142,15 @@
         <v>800</v>
       </c>
       <c r="E60" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B61">
         <v>450</v>
@@ -2002,12 +2162,15 @@
         <v>600</v>
       </c>
       <c r="E61" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="B62">
         <v>700</v>
@@ -2019,12 +2182,15 @@
         <v>1000</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B63">
         <v>1500</v>
@@ -2036,12 +2202,15 @@
         <v>2500</v>
       </c>
       <c r="E63" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B64">
         <v>1100</v>
@@ -2053,12 +2222,15 @@
         <v>1800</v>
       </c>
       <c r="E64" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B65">
         <v>1200</v>
@@ -2070,12 +2242,15 @@
         <v>1600</v>
       </c>
       <c r="E65" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F65" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B66">
         <v>1300</v>
@@ -2087,12 +2262,15 @@
         <v>1700</v>
       </c>
       <c r="E66" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="B67">
         <v>2200</v>
@@ -2104,12 +2282,15 @@
         <v>3200</v>
       </c>
       <c r="E67" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F67" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B68">
         <v>1400</v>
@@ -2121,12 +2302,15 @@
         <v>2000</v>
       </c>
       <c r="E68" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F68" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="B69">
         <v>1600</v>
@@ -2138,12 +2322,15 @@
         <v>2000</v>
       </c>
       <c r="E69" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F69" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="B70">
         <v>1300</v>
@@ -2155,12 +2342,15 @@
         <v>1700</v>
       </c>
       <c r="E70" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F70" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B71">
         <v>1200</v>
@@ -2172,12 +2362,15 @@
         <v>1600</v>
       </c>
       <c r="E71" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F71" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B72">
         <v>2200</v>
@@ -2189,12 +2382,15 @@
         <v>4000</v>
       </c>
       <c r="E72" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F72" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="B73">
         <v>1300</v>
@@ -2206,12 +2402,15 @@
         <v>1700</v>
       </c>
       <c r="E73" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B74">
         <v>1300</v>
@@ -2223,12 +2422,15 @@
         <v>1700</v>
       </c>
       <c r="E74" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F74" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B75">
         <v>1300</v>
@@ -2240,12 +2442,15 @@
         <v>1700</v>
       </c>
       <c r="E75" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F75" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B76">
         <v>1300</v>
@@ -2257,12 +2462,15 @@
         <v>1700</v>
       </c>
       <c r="E76" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F76" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="B77">
         <v>1800</v>
@@ -2274,12 +2482,15 @@
         <v>2800</v>
       </c>
       <c r="E77" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F77" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="B78">
         <v>1200</v>
@@ -2291,29 +2502,35 @@
         <v>1600</v>
       </c>
       <c r="E78" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="B79" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C79" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D79" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="E79" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F79" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="B80">
         <v>1300</v>
@@ -2325,12 +2542,15 @@
         <v>1700</v>
       </c>
       <c r="E80" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F80" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B81">
         <v>1300</v>
@@ -2342,12 +2562,15 @@
         <v>1700</v>
       </c>
       <c r="E81" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F81" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="B82">
         <v>1400</v>
@@ -2359,12 +2582,15 @@
         <v>2000</v>
       </c>
       <c r="E82" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B83">
         <v>1400</v>
@@ -2376,12 +2602,15 @@
         <v>2000</v>
       </c>
       <c r="E83" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B84">
         <v>1800</v>
@@ -2393,26 +2622,32 @@
         <v>2600</v>
       </c>
       <c r="E84" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="C85" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="D85" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+      <c r="F85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="B86">
         <v>1400</v>
@@ -2424,12 +2659,15 @@
         <v>2000</v>
       </c>
       <c r="E86" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="F86" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B87">
         <v>1300</v>
@@ -2441,312 +2679,369 @@
         <v>1800</v>
       </c>
       <c r="E87" t="s">
+        <v>76</v>
+      </c>
+      <c r="F87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s">
+        <v>102</v>
+      </c>
+      <c r="C88" t="s">
+        <v>102</v>
+      </c>
+      <c r="D88" t="s">
+        <v>102</v>
+      </c>
+      <c r="E88" t="s">
+        <v>7</v>
+      </c>
+      <c r="F88" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>104</v>
+      </c>
+      <c r="B89" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" t="s">
+        <v>102</v>
+      </c>
+      <c r="D89" t="s">
+        <v>102</v>
+      </c>
+      <c r="E89" t="s">
+        <v>7</v>
+      </c>
+      <c r="F89" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>105</v>
+      </c>
+      <c r="B90" t="s">
+        <v>102</v>
+      </c>
+      <c r="C90" t="s">
+        <v>102</v>
+      </c>
+      <c r="D90" t="s">
+        <v>102</v>
+      </c>
+      <c r="E90" t="s">
+        <v>7</v>
+      </c>
+      <c r="F90" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>106</v>
+      </c>
+      <c r="B91" t="s">
+        <v>102</v>
+      </c>
+      <c r="C91" t="s">
+        <v>102</v>
+      </c>
+      <c r="D91" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>107</v>
+      </c>
+      <c r="B92" t="s">
+        <v>102</v>
+      </c>
+      <c r="C92" t="s">
+        <v>102</v>
+      </c>
+      <c r="D92" t="s">
+        <v>102</v>
+      </c>
+      <c r="E92" t="s">
+        <v>7</v>
+      </c>
+      <c r="F92" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B93" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" t="s">
+        <v>102</v>
+      </c>
+      <c r="D93" t="s">
+        <v>102</v>
+      </c>
+      <c r="F93" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>109</v>
+      </c>
+      <c r="B94" t="s">
+        <v>102</v>
+      </c>
+      <c r="C94" t="s">
+        <v>102</v>
+      </c>
+      <c r="D94" t="s">
+        <v>102</v>
+      </c>
+      <c r="E94" t="s">
+        <v>7</v>
+      </c>
+      <c r="F94" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>110</v>
+      </c>
+      <c r="B95" t="s">
+        <v>102</v>
+      </c>
+      <c r="C95" t="s">
+        <v>102</v>
+      </c>
+      <c r="D95" t="s">
+        <v>102</v>
+      </c>
+      <c r="E95" t="s">
+        <v>7</v>
+      </c>
+      <c r="F95" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>111</v>
+      </c>
+      <c r="B96" t="s">
+        <v>102</v>
+      </c>
+      <c r="C96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" t="s">
+        <v>102</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>112</v>
+      </c>
+      <c r="B97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C97" t="s">
+        <v>102</v>
+      </c>
+      <c r="D97" t="s">
+        <v>102</v>
+      </c>
+      <c r="E97" t="s">
+        <v>7</v>
+      </c>
+      <c r="F97" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>113</v>
+      </c>
+      <c r="B98" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" t="s">
+        <v>102</v>
+      </c>
+      <c r="D98" t="s">
+        <v>102</v>
+      </c>
+      <c r="E98" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>114</v>
+      </c>
+      <c r="B99" t="s">
+        <v>102</v>
+      </c>
+      <c r="C99" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" t="s">
+        <v>102</v>
+      </c>
+      <c r="E99" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>115</v>
+      </c>
+      <c r="B100" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" t="s">
+        <v>102</v>
+      </c>
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>116</v>
+      </c>
+      <c r="B101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101" t="s">
+        <v>102</v>
+      </c>
+      <c r="D101" t="s">
+        <v>102</v>
+      </c>
+      <c r="F101" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>117</v>
+      </c>
+      <c r="B102" t="s">
+        <v>102</v>
+      </c>
+      <c r="C102" t="s">
+        <v>102</v>
+      </c>
+      <c r="D102" t="s">
+        <v>102</v>
+      </c>
+      <c r="E102" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>119</v>
+      </c>
+      <c r="B103" t="s">
+        <v>102</v>
+      </c>
+      <c r="C103" t="s">
+        <v>102</v>
+      </c>
+      <c r="D103" t="s">
+        <v>102</v>
+      </c>
+      <c r="E103" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88" t="s">
-        <v>116</v>
-      </c>
-      <c r="C88" t="s">
-        <v>116</v>
-      </c>
-      <c r="D88" t="s">
-        <v>116</v>
-      </c>
-      <c r="E88" t="s">
+      <c r="B104" t="s">
+        <v>102</v>
+      </c>
+      <c r="C104" t="s">
+        <v>102</v>
+      </c>
+      <c r="D104" t="s">
+        <v>102</v>
+      </c>
+      <c r="E104" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89" t="s">
-        <v>116</v>
-      </c>
-      <c r="C89" t="s">
-        <v>116</v>
-      </c>
-      <c r="D89" t="s">
-        <v>116</v>
-      </c>
-      <c r="E89" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>121</v>
+      </c>
+      <c r="B105" t="s">
+        <v>102</v>
+      </c>
+      <c r="C105" t="s">
+        <v>102</v>
+      </c>
+      <c r="D105" t="s">
+        <v>102</v>
+      </c>
+      <c r="E105" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" t="s">
-        <v>116</v>
-      </c>
-      <c r="C90" t="s">
-        <v>116</v>
-      </c>
-      <c r="D90" t="s">
-        <v>116</v>
-      </c>
-      <c r="E90" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" t="s">
-        <v>116</v>
-      </c>
-      <c r="C91" t="s">
-        <v>116</v>
-      </c>
-      <c r="D91" t="s">
-        <v>116</v>
-      </c>
-      <c r="E91" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92" t="s">
-        <v>116</v>
-      </c>
-      <c r="C92" t="s">
-        <v>116</v>
-      </c>
-      <c r="D92" t="s">
-        <v>116</v>
-      </c>
-      <c r="E92" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" t="s">
-        <v>116</v>
-      </c>
-      <c r="C93" t="s">
-        <v>116</v>
-      </c>
-      <c r="D93" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" t="s">
-        <v>116</v>
-      </c>
-      <c r="C94" t="s">
-        <v>116</v>
-      </c>
-      <c r="D94" t="s">
-        <v>116</v>
-      </c>
-      <c r="E94" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" t="s">
-        <v>116</v>
-      </c>
-      <c r="C95" t="s">
-        <v>116</v>
-      </c>
-      <c r="D95" t="s">
-        <v>116</v>
-      </c>
-      <c r="E95" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" t="s">
-        <v>116</v>
-      </c>
-      <c r="C96" t="s">
-        <v>116</v>
-      </c>
-      <c r="D96" t="s">
-        <v>116</v>
-      </c>
-      <c r="E96" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" t="s">
-        <v>116</v>
-      </c>
-      <c r="C97" t="s">
-        <v>116</v>
-      </c>
-      <c r="D97" t="s">
-        <v>116</v>
-      </c>
-      <c r="E97" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>101</v>
-      </c>
-      <c r="B98" t="s">
-        <v>116</v>
-      </c>
-      <c r="C98" t="s">
-        <v>116</v>
-      </c>
-      <c r="D98" t="s">
-        <v>116</v>
-      </c>
-      <c r="E98" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>102</v>
-      </c>
-      <c r="B99" t="s">
-        <v>116</v>
-      </c>
-      <c r="C99" t="s">
-        <v>116</v>
-      </c>
-      <c r="D99" t="s">
-        <v>116</v>
-      </c>
-      <c r="E99" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>103</v>
-      </c>
-      <c r="B100" t="s">
-        <v>116</v>
-      </c>
-      <c r="C100" t="s">
-        <v>116</v>
-      </c>
-      <c r="D100" t="s">
-        <v>116</v>
-      </c>
-      <c r="E100" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>104</v>
-      </c>
-      <c r="B101" t="s">
-        <v>116</v>
-      </c>
-      <c r="C101" t="s">
-        <v>116</v>
-      </c>
-      <c r="D101" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>105</v>
-      </c>
-      <c r="B102" t="s">
-        <v>116</v>
-      </c>
-      <c r="C102" t="s">
-        <v>116</v>
-      </c>
-      <c r="D102" t="s">
-        <v>116</v>
-      </c>
-      <c r="E102" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>106</v>
-      </c>
-      <c r="B103" t="s">
-        <v>116</v>
-      </c>
-      <c r="C103" t="s">
-        <v>116</v>
-      </c>
-      <c r="D103" t="s">
-        <v>116</v>
-      </c>
-      <c r="E103" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" t="s">
-        <v>116</v>
-      </c>
-      <c r="C104" t="s">
-        <v>116</v>
-      </c>
-      <c r="D104" t="s">
-        <v>116</v>
-      </c>
-      <c r="E104" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>108</v>
-      </c>
-      <c r="B105" t="s">
-        <v>116</v>
-      </c>
-      <c r="C105" t="s">
-        <v>116</v>
-      </c>
-      <c r="D105" t="s">
-        <v>116</v>
-      </c>
-      <c r="E105" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B106">
         <v>2300</v>
@@ -2758,12 +3053,15 @@
         <v>3000</v>
       </c>
       <c r="E106" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="F106" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="B107">
         <v>2300</v>
@@ -2775,12 +3073,15 @@
         <v>3000</v>
       </c>
       <c r="E107" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="F107" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B108">
         <v>2300</v>
@@ -2792,12 +3093,15 @@
         <v>3000</v>
       </c>
       <c r="E108" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="F108" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="B109">
         <v>2500</v>
@@ -2809,12 +3113,15 @@
         <v>3900</v>
       </c>
       <c r="E109" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="F109" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="B110">
         <v>2400</v>
@@ -2826,43 +3133,45 @@
         <v>3800</v>
       </c>
       <c r="E110" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="F110" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AC098A7-35A7-4BCD-91EC-EB47DF3230D8}">
-  <dimension ref="A1:A36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EBBFACB-A8ED-4369-8AE2-A8BC12839CBF}">
+  <dimension ref="A1:A35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
@@ -2872,142 +3181,137 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3016,123 +3320,123 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D914AB9D-DF70-4D46-B99B-52B39621BD8C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B8DB0A6-B073-452A-931A-BBBE7DA35FCB}">
   <dimension ref="A1:A28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
